--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -7,8 +7,7 @@
     <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="普通装备" sheetId="1" r:id="rId1"/>
-    <sheet name="特殊装备" sheetId="2" r:id="rId2"/>
+    <sheet name="特殊装备" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
   <si>
     <t>_Id</t>
   </si>
@@ -36,15 +35,24 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AttrId</t>
-  </si>
-  <si>
-    <t>AttrValue</t>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>AtrIdList</t>
+  </si>
+  <si>
+    <t>AtrVueList</t>
+  </si>
+  <si>
+    <t>RiseList</t>
   </si>
   <si>
     <t>BuffId</t>
   </si>
   <si>
+    <t>Desc</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -54,34 +62,49 @@
     <t>string</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>Cycle</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>AttrRise</t>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>金币加成</t>
-  </si>
-  <si>
-    <t>经验加成</t>
-  </si>
-  <si>
-    <t>品质加成</t>
-  </si>
-  <si>
-    <t>爆率加成</t>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>double[]</t>
+  </si>
+  <si>
+    <t>治愈之心</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>恢复加成+{0}%</t>
+  </si>
+  <si>
+    <t>聚宝盆</t>
+  </si>
+  <si>
+    <t>85,81</t>
+  </si>
+  <si>
+    <t>100,10</t>
+  </si>
+  <si>
+    <t>1,0.1</t>
+  </si>
+  <si>
+    <t>杀敌金币+{0},金币加成+{1}%</t>
+  </si>
+  <si>
+    <t>聚灵阵</t>
+  </si>
+  <si>
+    <t>86,82</t>
+  </si>
+  <si>
+    <t>杀敌经验+{0},经验加成+{1}%</t>
   </si>
 </sst>
 </file>
@@ -720,6 +743,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1039,310 +1063,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="C3:J8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="18.8333333333333" style="1" customWidth="1"/>
-    <col min="5" max="6" width="13.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.75" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" customHeight="1" spans="3:7">
-      <c r="C3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:7">
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="3:7">
-      <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:7">
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1">
-        <v>100</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:7">
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="E7" s="1">
-        <v>81</v>
-      </c>
-      <c r="F7" s="1">
-        <v>20</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:7">
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1">
-        <v>82</v>
-      </c>
-      <c r="F8" s="1">
-        <v>20</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 C3:C5 D4:D5" errorStyle="warning">
-      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="C1:J9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
-  <cols>
-    <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="6" width="16.25" style="1" customWidth="1"/>
-    <col min="7" max="8" width="13.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
+    <col min="4" max="5" width="16.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="8" width="16.4166666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.0833333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.5833333333333" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C5" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C6" s="1">
-        <v>1001</v>
-      </c>
-      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="1">
         <v>0</v>
       </c>
-      <c r="E6" s="1">
-        <v>101</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>81</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
       <c r="J6" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C7" s="1">
-        <v>1002</v>
-      </c>
-      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="1">
         <v>0</v>
       </c>
-      <c r="E7" s="1">
-        <v>101</v>
-      </c>
-      <c r="F7" s="1">
-        <v>2</v>
-      </c>
-      <c r="G7" s="1">
-        <v>82</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
       <c r="J7" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C8" s="1">
-        <v>1003</v>
-      </c>
-      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="1">
         <v>0</v>
       </c>
-      <c r="E8" s="1">
-        <v>101</v>
-      </c>
-      <c r="F8" s="1">
-        <v>3</v>
-      </c>
-      <c r="G8" s="1">
-        <v>83</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
       <c r="J8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C9" s="1">
-        <v>1004</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>101</v>
-      </c>
-      <c r="F9" s="1">
-        <v>4</v>
-      </c>
-      <c r="G9" s="1">
-        <v>84</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -74,7 +74,7 @@
     <t>15</t>
   </si>
   <si>
-    <t>100</t>
+    <t>60</t>
   </si>
   <si>
     <t>1</t>
@@ -89,7 +89,7 @@
     <t>85,81</t>
   </si>
   <si>
-    <t>100,10</t>
+    <t>60,10</t>
   </si>
   <si>
     <t>1,0.1</t>

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -74,10 +74,10 @@
     <t>15</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>0.5</t>
   </si>
   <si>
     <t>恢复加成+{0}%</t>
@@ -89,7 +89,7 @@
     <t>85,81</t>
   </si>
   <si>
-    <t>60,10</t>
+    <t>40,5</t>
   </si>
   <si>
     <t>1,0.1</t>

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
   <si>
     <t>_Id</t>
   </si>
@@ -98,13 +98,28 @@
     <t>杀敌金币+{0},金币加成+{1}%</t>
   </si>
   <si>
-    <t>聚灵阵</t>
+    <t>夺灵阵</t>
   </si>
   <si>
     <t>86,82</t>
   </si>
   <si>
     <t>杀敌经验+{0},经验加成+{1}%</t>
+  </si>
+  <si>
+    <t>狂风之心</t>
+  </si>
+  <si>
+    <t>10,11</t>
+  </si>
+  <si>
+    <t>10,10</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>攻击速度+{0},技能冷却+{1}%</t>
   </si>
 </sst>
 </file>
@@ -1063,8 +1078,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelRow="7"/>
+  <dimension ref="C3:J9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="5" width="16.25" style="1" customWidth="1"/>
@@ -1231,6 +1246,32 @@
         <v>25</v>
       </c>
     </row>
+    <row r="9" customHeight="1" spans="3:10">
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5" errorStyle="warning">

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>_Id</t>
   </si>
@@ -120,6 +120,18 @@
   </si>
   <si>
     <t>攻击速度+{0},技能冷却+{1}%</t>
+  </si>
+  <si>
+    <t>重击战法</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>弱点追踪</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -1078,7 +1090,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J9"/>
+  <dimension ref="C3:J11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1272,6 +1284,40 @@
         <v>30</v>
       </c>
     </row>
+    <row r="10" customHeight="1" spans="3:10">
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:10">
+      <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5" errorStyle="warning">

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
   <si>
     <t>_Id</t>
   </si>
@@ -47,9 +47,6 @@
     <t>RiseList</t>
   </si>
   <si>
-    <t>BuffId</t>
-  </si>
-  <si>
     <t>Desc</t>
   </si>
   <si>
@@ -125,13 +122,52 @@
     <t>重击战法</t>
   </si>
   <si>
-    <t>0.1</t>
+    <t>30001,30002</t>
+  </si>
+  <si>
+    <t>10,100</t>
+  </si>
+  <si>
+    <t>0.1,1</t>
+  </si>
+  <si>
+    <t>{0}%的概率使伤害提高{1}%</t>
   </si>
   <si>
     <t>弱点追踪</t>
   </si>
   <si>
-    <t>1</t>
+    <t>30011</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>触发暴击时，伤害提高{0}%</t>
+  </si>
+  <si>
+    <t>天命</t>
+  </si>
+  <si>
+    <t>30022,30024,30026,30028,30030</t>
+  </si>
+  <si>
+    <t>10000,1000,100,10,50</t>
+  </si>
+  <si>
+    <t>100,10,1,0.1,-0.5</t>
+  </si>
+  <si>
+    <t>最终伤害有0.1%提高{0}%，1%提高{1}%，10%提高{2}%，40%提高{3}%，48.9%降低{4}%</t>
+  </si>
+  <si>
+    <t>致命节奏</t>
+  </si>
+  <si>
+    <t>30031</t>
+  </si>
+  <si>
+    <t>触发致命时，伤害提高{0}%</t>
   </si>
 </sst>
 </file>
@@ -144,7 +180,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,6 +199,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -634,142 +676,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1090,19 +1134,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J11"/>
+  <dimension ref="C3:I18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="5" width="16.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="8" width="16.4166666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.0833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.5833333333333" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="33.9166666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.4166666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="82.75" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1124,13 +1168,10 @@
       <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="2" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C4" s="2" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C4" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
@@ -1150,173 +1191,228 @@
       <c r="I4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:10">
+    </row>
+    <row r="9" customHeight="1" spans="3:9">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:10">
+    </row>
+    <row r="10" customHeight="1" spans="3:9">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="F10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:10">
+      <c r="H10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:9">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="1">
-        <v>2</v>
-      </c>
+      <c r="F11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:9">
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:9">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:9">
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" customHeight="1" spans="3:9">
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" customHeight="1" spans="3:9">
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" customHeight="1" spans="9:9">
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" customHeight="1" spans="9:9">
+      <c r="I18" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>_Id</t>
   </si>
@@ -71,7 +71,7 @@
     <t>15</t>
   </si>
   <si>
-    <t>30</t>
+    <t>20</t>
   </si>
   <si>
     <t>0.5</t>
@@ -86,7 +86,7 @@
     <t>85,81</t>
   </si>
   <si>
-    <t>40,5</t>
+    <t>20,3</t>
   </si>
   <si>
     <t>1,0.1</t>
@@ -125,7 +125,7 @@
     <t>30001,30002</t>
   </si>
   <si>
-    <t>10,100</t>
+    <t>10,50</t>
   </si>
   <si>
     <t>0.1,1</t>
@@ -138,9 +138,6 @@
   </si>
   <si>
     <t>30011</t>
-  </si>
-  <si>
-    <t>20</t>
   </si>
   <si>
     <t>触发暴击时，伤害提高{0}%</t>
@@ -1344,13 +1341,13 @@
         <v>36</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>15</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:9">
@@ -1358,22 +1355,22 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
       </c>
       <c r="F12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:9">
@@ -1381,22 +1378,22 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>15</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:9">

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -113,10 +113,10 @@
     <t>10,10</t>
   </si>
   <si>
-    <t>1,1</t>
-  </si>
-  <si>
-    <t>攻击速度+{0},技能冷却+{1}%</t>
+    <t>0.2,0.2</t>
+  </si>
+  <si>
+    <t>攻击速度+{0}%,技能冷却+{1}%</t>
   </si>
   <si>
     <t>重击战法</t>

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -110,10 +115,10 @@
     <t>10,11</t>
   </si>
   <si>
-    <t>10,10</t>
-  </si>
-  <si>
-    <t>0.2,0.2</t>
+    <t>8,8</t>
+  </si>
+  <si>
+    <t>0.15,0.15</t>
   </si>
   <si>
     <t>攻击速度+{0}%,技能冷却+{1}%</t>

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -118,7 +118,7 @@
     <t>8,8</t>
   </si>
   <si>
-    <t>0.15,0.15</t>
+    <t>0.1,0.1</t>
   </si>
   <si>
     <t>攻击速度+{0}%,技能冷却+{1}%</t>

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="特殊装备" sheetId="2" r:id="rId1"/>
@@ -148,6 +148,15 @@
     <t>触发暴击时，伤害提高{0}%</t>
   </si>
   <si>
+    <t>致命节奏</t>
+  </si>
+  <si>
+    <t>30031</t>
+  </si>
+  <si>
+    <t>触发致命时，伤害提高{0}%</t>
+  </si>
+  <si>
     <t>天命</t>
   </si>
   <si>
@@ -161,15 +170,6 @@
   </si>
   <si>
     <t>最终伤害有0.1%提高{0}%，1%提高{1}%，10%提高{2}%，40%提高{3}%，48.9%降低{4}%</t>
-  </si>
-  <si>
-    <t>致命节奏</t>
-  </si>
-  <si>
-    <t>30031</t>
-  </si>
-  <si>
-    <t>触发致命时，伤害提高{0}%</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1136,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I18"/>
+  <dimension ref="C3:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1369,13 +1369,13 @@
         <v>39</v>
       </c>
       <c r="G12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:9">
@@ -1383,21 +1383,21 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="4" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1413,9 +1413,6 @@
     <row r="17" customHeight="1" spans="9:9">
       <c r="I17" s="4"/>
     </row>
-    <row r="18" customHeight="1" spans="9:9">
-      <c r="I18" s="4"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5" errorStyle="warning">

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="特殊装备" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
   <si>
     <t>_Id</t>
   </si>
@@ -170,6 +170,30 @@
   </si>
   <si>
     <t>最终伤害有0.1%提高{0}%，1%提高{1}%，10%提高{2}%，40%提高{3}%，48.9%降低{4}%</t>
+  </si>
+  <si>
+    <t>福运</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>品质加成+{1}%</t>
+  </si>
+  <si>
+    <t>寻宝</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>爆率加成+{1}%</t>
   </si>
 </sst>
 </file>
@@ -1402,10 +1426,50 @@
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:9">
-      <c r="I14" s="4"/>
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="1">
+        <v>3</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="15" customHeight="1" spans="3:9">
-      <c r="I15" s="4"/>
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="16" customHeight="1" spans="3:9">
       <c r="I16" s="4"/>

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -184,7 +184,7 @@
     <t>0.1</t>
   </si>
   <si>
-    <t>品质加成+{1}%</t>
+    <t>品质加成+{0}%</t>
   </si>
   <si>
     <t>寻宝</t>
@@ -193,7 +193,7 @@
     <t>84</t>
   </si>
   <si>
-    <t>爆率加成+{1}%</t>
+    <t>爆率加成+{0}%</t>
   </si>
 </sst>
 </file>

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
   <si>
     <t>_Id</t>
   </si>
@@ -178,7 +178,7 @@
     <t>83</t>
   </si>
   <si>
-    <t>3</t>
+    <t>5</t>
   </si>
   <si>
     <t>0.1</t>
@@ -194,6 +194,24 @@
   </si>
   <si>
     <t>爆率加成+{0}%</t>
+  </si>
+  <si>
+    <t>背刺</t>
+  </si>
+  <si>
+    <t>30041</t>
+  </si>
+  <si>
+    <t>首次攻击对敌人造成{0}%生命上限的额外伤害</t>
+  </si>
+  <si>
+    <t>斩杀</t>
+  </si>
+  <si>
+    <t>30051</t>
+  </si>
+  <si>
+    <t>敌人生命低于{0}%的时候，直接斩杀敌人</t>
   </si>
 </sst>
 </file>
@@ -1472,10 +1490,50 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:9">
-      <c r="I16" s="4"/>
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="17" customHeight="1" spans="9:9">
-      <c r="I17" s="4"/>
+    <row r="17" customHeight="1" spans="3:9">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
